--- a/EKG_Kalite_Yönetim_Sistemi/13_Giriş Lojistiği ve Depolama/03_ILG3 - Depolama, FIFO ve Raf Ömrü/EKG-LOJ-FRM-03_devirli_sayim_ve_hareketsiz_stok_karar_kaydi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/13_Giriş Lojistiği ve Depolama/03_ILG3 - Depolama, FIFO ve Raf Ömrü/EKG-LOJ-FRM-03_devirli_sayim_ve_hareketsiz_stok_karar_kaydi.xlsx
@@ -774,7 +774,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-FRM-03&amp;C&amp;"Arial,Regular"&amp;11Devirli Sayım ve Hareketsiz Stok Karar Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 24.09.2026
+Revizyon nedeni: Sayım farkı ve doğruluk hesapları düzeltildi; hareketsiz stok değerlendirmesi kayıt tarihine bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -988,7 +989,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-FRM-03&amp;C&amp;"Arial,Regular"&amp;11Devirli Sayım ve Hareketsiz Stok Karar Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 24.09.2026
+Revizyon nedeni: Sayım farkı ve doğruluk hesapları düzeltildi; hareketsiz stok değerlendirmesi kayıt tarihine bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>